--- a/AAII_Financials/Quarterly/SYY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SYY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
   <si>
     <t>SYY</t>
   </si>
@@ -656,539 +656,552 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E7" s="2">
         <v>46109</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46018</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45927</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45836</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45745</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45654</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45563</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45472</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45381</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45290</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45108</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45017</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44835</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44744</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44653</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44562</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44471</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44380</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44282</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44191</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44009</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43918</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43827</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43736</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43645</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43554</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43463</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43372</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43099</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42917</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42826</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>22124000</v>
+      </c>
+      <c r="E8" s="3">
         <v>20519000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>20762000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>21148000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>21138000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>19598000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>20151000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20484000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20556000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19380000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19288000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>19620000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>19728500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>18875700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>18594000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>19126800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>18957300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>16902100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>16320200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>16456500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>16136900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11824600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11559000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>11777400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8866600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>13698700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>15025000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>15303000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>15474900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>14658100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>14765700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>15215300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>15315900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>14349500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>14411500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>14650400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>14421000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>13524200</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>13457300</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>13968700</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>17990000</v>
+      </c>
+      <c r="E9" s="3">
         <v>16707000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>16970000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>17247000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>17152000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16017000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>16501000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16731000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>16718000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15771000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15774000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>15972000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>16043800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15444300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>15244300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>15638000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>15513000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>13888700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>13429100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>13484800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>13221100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9701900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>9460500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>9557500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>7300900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>11134500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>12196600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>12359600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>12495700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>11903800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>11994000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>12311500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>12399200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>11673900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>11712100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>11856800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>11661500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>10990000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>10885400</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>11276700</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4134000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3812000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3792000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3901000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3986000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3581000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3650000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3753000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3838000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3609000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3514000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3648000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3684700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3431400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3349700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3488800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3444300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3013400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2891100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2971700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2915800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2122700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2098500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2219900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1565700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2564200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2828400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2943400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2979200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2754300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2771700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2903800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2916700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2675600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2699400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2793600</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>2759500</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>2534200</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>2571900</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>2692000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1231,8 +1244,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1353,8 +1367,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1475,55 +1492,58 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>119000</v>
+      </c>
+      <c r="E14" s="3">
         <v>108000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>115000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>68000</v>
       </c>
-      <c r="G14" s="3">
-        <v>305000</v>
-      </c>
       <c r="H14" s="3">
+        <v>175000</v>
+      </c>
+      <c r="I14" s="3">
         <v>60000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>71000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>37000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>198000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>44000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>45000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>50000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-65800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>42800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>315400</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
@@ -1549,11 +1569,11 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
         <v>259100</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
@@ -1567,8 +1587,8 @@
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -1597,53 +1617,56 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E15" s="3">
         <v>42000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>240000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>31000</v>
       </c>
-      <c r="G15" s="3">
-        <v>-27000</v>
-      </c>
       <c r="H15" s="3">
+        <v>106000</v>
+      </c>
+      <c r="I15" s="3">
         <v>32000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>238000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>32000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-31000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>32000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>219000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>206000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>50000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>196000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1653,8 +1676,8 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>8</v>
+      <c r="U15" s="3">
+        <v>0</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>8</v>
@@ -1671,20 +1694,20 @@
       <c r="Z15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AA15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB15" s="3">
         <v>10700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>8700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>10300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>8600</v>
-      </c>
-      <c r="AE15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF15" s="3" t="s">
         <v>8</v>
@@ -1698,8 +1721,8 @@
       <c r="AI15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ15" s="3">
-        <v>0</v>
+      <c r="AJ15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK15" s="3">
         <v>0</v>
@@ -1719,8 +1742,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1760,252 +1786,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>21052000</v>
+      </c>
+      <c r="E17" s="3">
         <v>19750000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>19934000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>20265000</v>
       </c>
-      <c r="G17" s="3">
-        <v>19966000</v>
-      </c>
       <c r="H17" s="3">
+        <v>20122000</v>
+      </c>
+      <c r="I17" s="3">
         <v>18864000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>19375000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>19650000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>19414000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>18620000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>18550000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>18766000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>18731600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>18146200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18268700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>18390000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>18183100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>16406400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15875300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>15824900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>15567200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>11588700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>11346900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>11357800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9454000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>13638400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>14472500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>14634700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>14754300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>14128500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>14313800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>14587100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>14628200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>13863600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>13879200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>14031100</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>13863100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>13088200</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>12964900</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>13401800</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1072000</v>
+      </c>
+      <c r="E18" s="3">
         <v>769000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>828000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>883000</v>
       </c>
-      <c r="G18" s="3">
-        <v>1172000</v>
-      </c>
       <c r="H18" s="3">
+        <v>1016000</v>
+      </c>
+      <c r="I18" s="3">
         <v>734000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>776000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>834000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1142000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>760000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>738000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>854000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>997000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>729500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>325300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>736800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>774200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>495700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>444900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>631600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>569700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>235900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>212100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>419600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-587400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>60300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>552500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>668300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>720600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>529600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>451900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>628200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>687700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>485900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>532300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>619300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>557900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>436000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>492400</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>566900</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2048,618 +2081,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E20" s="3">
         <v>48000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>30000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>43000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-15000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="I20" s="3">
         <v>2000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>12000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-25000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>7000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-30700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-14800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-17700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>13800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>10700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>13500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>12700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>15500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-20700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>15500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-19200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-13700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-19000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>34100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-26900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-27600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-20600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-22900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>1500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-11700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-8500</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>100</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>3100</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-200</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1164000</v>
+      </c>
+      <c r="E21" s="3">
         <v>763000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1038000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>871000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1160000</v>
-      </c>
       <c r="H21" s="3">
+        <v>1163000</v>
+      </c>
+      <c r="I21" s="3">
         <v>764000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1002000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>871000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1136000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>788000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>959000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1053000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1077700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>927800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>500500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>908000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>971700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>703400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>646900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>821400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>778600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>425800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>412400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>579400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-324800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>227200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>723700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>836700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>942000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>686900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>629000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>795200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>866500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>680800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>711300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>790500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>792800</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>657400</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>729600</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>782300</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>205000</v>
+      </c>
+      <c r="E22" s="3">
         <v>168000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>173000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>172000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>166000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>149000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>160000</v>
       </c>
       <c r="J22" s="3">
         <v>160000</v>
       </c>
       <c r="K22" s="3">
+        <v>160000</v>
+      </c>
+      <c r="L22" s="3">
         <v>165000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>158000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>150000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>134000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>135900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>134900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>132000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>124200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>128500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>124000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>242900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>128200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>441100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>145800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>146500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>140200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>164300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>69800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>62200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>67500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>72400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>71700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>69700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>69600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>71600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>122500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>68900</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>64400</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>74500</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>79300</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>69800</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>70200</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>720000</v>
+      </c>
+      <c r="E23" s="3">
         <v>445000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>510000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>600000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>716000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>523000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>533000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>642000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>804000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>554000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>545000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>663000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>957600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>554000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>178500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>594900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>641900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>385500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>212700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>506700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>142000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>102900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>81100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>258700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-736200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-28800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>476500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>581900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>682300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>431000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>354600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>538000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>593200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>364900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>451700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>546500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>483500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>359800</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>422500</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>500400</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>169000</v>
+      </c>
+      <c r="E24" s="3">
         <v>105000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>121000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>124000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>185000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>122000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>127000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>152000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>192000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>129000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>130000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>160000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>224000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>124400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>37300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>129300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>131900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>82200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>45200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>128700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-9100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>13900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>13800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>41800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-117800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-25500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>93100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>128100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>143900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-8900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>75300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>107000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>142700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>34800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>236800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>178800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>178400</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>121500</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>147300</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>176500</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2780,252 +2829,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>551000</v>
+      </c>
+      <c r="E26" s="3">
         <v>340000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>389000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>476000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>531000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>401000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>406000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>490000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>612000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>425000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>415000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>503000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>733600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>429600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>141200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>465600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>510000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>303300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>167400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>378000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>151100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>88900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>67300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>216900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-618400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>383400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>453800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>538400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>439800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>279300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>431000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>450400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>330100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>214900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>367600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>305200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>238300</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>275200</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>323900</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>551000</v>
+      </c>
+      <c r="E27" s="3">
         <v>340000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>389000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>476000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>531000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>401000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>406000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>490000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>612000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>425000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>415000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>503000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>733600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>429600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>141200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>465600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>510000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>303300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>167400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>378000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>151100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>88900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>67300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>216900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-618400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>383400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>453800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>538400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>439800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>279300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>431000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>450400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>330100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>214900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>367600</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>305200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>238300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>275200</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>323900</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3146,8 +3204,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3214,14 +3275,14 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB29" s="3">
         <v>0</v>
@@ -3229,32 +3290,32 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>300</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-11900</v>
       </c>
-      <c r="AH29" s="3" t="s">
+      <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-1500</v>
       </c>
-      <c r="AJ29" s="3" t="s">
+      <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>69200</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3268,8 +3329,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3390,8 +3454,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3512,252 +3579,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-48000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-30000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-43000</v>
       </c>
-      <c r="G32" s="3">
-        <v>15000</v>
-      </c>
       <c r="H32" s="3">
+        <v>41000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-2000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-12000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>25000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-7000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>30700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>14800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>17700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-13800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-10700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-13500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-12700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-15500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>20700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-15500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>19200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>13700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>19000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-34100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>26900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>27600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>20600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>22900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>11700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>8500</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-100</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-3100</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>200</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>551000</v>
+      </c>
+      <c r="E33" s="3">
         <v>340000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>389000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>476000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>531000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>401000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>406000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>490000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>612000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>425000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>415000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>503000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>733600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>429600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>141200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>465600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>510000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>303300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>167400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>378000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>151100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>88900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>67300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>216900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-618400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>383400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>453800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>535800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>440100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>267400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>431000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>448900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>330100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>284100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>367600</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>305200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>238300</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>275200</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>323900</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3878,257 +3954,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>551000</v>
+      </c>
+      <c r="E35" s="3">
         <v>340000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>389000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>476000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>531000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>401000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>406000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>490000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>612000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>425000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>415000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>503000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>733600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>429600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>141200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>465600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>510000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>303300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>167400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>378000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>151100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>88900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>67300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>216900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-618400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>383400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>453800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>535800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>440100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>267400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>431000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>448900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>330100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>284100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>367600</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>305200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>238300</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>275200</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>323900</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E38" s="2">
         <v>46109</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46018</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45927</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45836</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45745</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45654</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45563</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45472</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45381</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45290</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45108</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45017</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44835</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44744</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44653</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44562</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44471</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44380</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44282</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44191</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44009</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43918</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43827</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43736</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43645</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43554</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43463</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43372</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43099</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42917</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42826</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4171,8 +4256,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4215,145 +4301,149 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1786000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1900000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1222000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>844000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1071000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1527000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>793000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>733000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>696000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>598300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>962200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>569100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>745000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>757900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>500300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>437700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>867100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>876100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1374300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2067900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3007100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4895700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5767000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5985500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6059400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2240800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>524600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>455500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>513500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>521600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>744800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>790300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>552300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>901600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>961100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>909200</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>869500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>855100</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>847300</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>759900</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E42" s="3">
         <v>2000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3000</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -4361,11 +4451,11 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>1000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -4459,528 +4549,543 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5886000</v>
+      </c>
+      <c r="E43" s="3">
         <v>5777000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5567000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5804000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5506000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5487000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5320000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5800000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5346000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5562500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5297400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5344500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5098000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5227400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4933600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5336900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4874800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4824800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4320800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4309900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3790300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3222200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2900000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3115800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3001600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3684600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4383300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4406900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4201400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4378100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4170400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4281800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>4137800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>4323500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3953600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>4333700</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>4029200</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>4386800</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>3990000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>4191500</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5338000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5291000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5260000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5377000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5053000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4893000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5050000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4991000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4678000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4734000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4722500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4648600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4481000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4620600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4661500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4682600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4437500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4409100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4115700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4054800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3695200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3218800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3100500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3134700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3095100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3697500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3508300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3386800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3216000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3344700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3310300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3354500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3125400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>3259800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>3174000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>3180600</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>2995600</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>2944300</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>3031500</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>3025800</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E45" s="3">
         <v>102000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>31000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>37000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>26000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>35000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>22000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>26000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>31000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>31800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>26700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>32500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>14000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>300500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>310100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>303800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>303200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>252400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>255600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>241000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>250000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>223900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>197100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>192200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>234900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>245500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>235000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>210600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>211200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>212300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>215700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>187900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>231100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>183400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>173500</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>139200</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>139300</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>142300</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>158300</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13437000</v>
+      </c>
+      <c r="E46" s="3">
         <v>13383000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12417000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12412000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11968000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12282000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11501000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11875000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11043000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11204900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11309600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10895700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10608000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10898600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10396000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>10767300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>10483200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>10413300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>10063200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>10688200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>10733600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>11586800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>11991400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>12433100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>12348200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>9857800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>8661600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>8484200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>8141500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>8455500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>8437800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>8642300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>8003500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>8715900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>8272200</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>8597000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>8033400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>8325600</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>8011200</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>8135500</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E47" s="3">
         <v>12000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>27000</v>
-      </c>
-      <c r="F47" s="3">
-        <v>31000</v>
       </c>
       <c r="G47" s="3">
         <v>31000</v>
       </c>
       <c r="H47" s="3">
+        <v>31000</v>
+      </c>
+      <c r="I47" s="3">
         <v>22000</v>
       </c>
-      <c r="I47" s="3" t="s">
+      <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>29000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>12100</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>8</v>
@@ -4991,8 +5096,8 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -5069,252 +5174,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7363000</v>
+      </c>
+      <c r="E48" s="3">
         <v>7208000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7258000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7108000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7215000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6815000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6620000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6566000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6420000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6172600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5981500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5795400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5647000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5358100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5271000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5167300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5179700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5132400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5032000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5093900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5035200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4959300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5018400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5025900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5062200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5225200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5224900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5119600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4501700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4377100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>4375600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>4466900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>4521700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>4392200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>4366300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>4388300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>4377300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>4271700</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>4331100</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>4418500</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6177000</v>
+      </c>
+      <c r="E49" s="3">
         <v>6241000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6327000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6233000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6311000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6299000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6263000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6422000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6341000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6357900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6429200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5594300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5506000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5500400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5488100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5340900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5495000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5746700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5323200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5330300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4690200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4702100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4728300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4570800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4512600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4665300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4879100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4697000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4753500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4812500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4775900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4881500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4935300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>5122300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>5057400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>5023300</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>4953600</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>4853900</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>4809300</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>5019600</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5435,8 +5549,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5557,130 +5674,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>901000</v>
+      </c>
+      <c r="E52" s="3">
         <v>651000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>657000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>770000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>752000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>473000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>493000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>524000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>662000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>522600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>576100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>566300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>640000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>509100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>932200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>935500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>927800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1031300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1008400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>990400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>954500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>795100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>751700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>711800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>705200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>684100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>606400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>655800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>569800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>555700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>604900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>551400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>610000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>398900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>523600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>410000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>392300</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>469800</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>478400</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>451300</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5801,130 +5924,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>28397000</v>
+      </c>
+      <c r="E54" s="3">
         <v>27983000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>27181000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>27044000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>26774000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>26347000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>25318000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>25880000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>24917000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>24712300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>24740600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>23272800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>22821000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>22702000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>22087200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>22210900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>22085700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>22323700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>21426800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>22102900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>21413500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>22043300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>22489900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>22741600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>22628300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>20432300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>19372000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>18956600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>17966500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>18200800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>18194200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>18542100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>18070400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>18629100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>18219400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>18418600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>17756700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>17920900</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>17630100</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>18024800</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5967,8 +6096,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6011,740 +6141,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6640000</v>
+      </c>
+      <c r="E57" s="3">
         <v>6387000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5954000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6492000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6512000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6183000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5842000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6374000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6290000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5869500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5737700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5796400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6025000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5902200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5420400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6018200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5753000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5721700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5019100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5238300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4884800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4221300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3554600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4035300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3447100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3969000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4159600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4247300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4314600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4293500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>4230200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>4217800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>4136500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>4235900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>3745800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>3951200</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>3971100</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>3849700</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>3549600</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>3716500</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1369000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1339000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1293000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2035000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1086000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1365000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1347000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>613000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>595000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>216200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>203900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>298600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>162000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>821700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>702100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>555800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>580600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>506700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>496000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>500100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>494900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>965600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1374900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1326000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1544400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>831900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>793700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>57800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>41300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>543000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>792100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>787400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>786500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>294700</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>541300</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>538200</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>534000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>551400</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>31500</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>16100</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>39000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>121000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>60000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>62000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>162000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>291000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>136000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>38000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>59300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>183900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>120000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>134600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2266000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2385200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2416500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2143800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2078500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1999500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1940100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1821100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1787100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1806700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1726400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1824100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1978700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1796400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1747300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1663700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1727800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1635700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1665800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1515700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1695800</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1650900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1590800</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1328800</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1471200</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1634000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10523000</v>
+      </c>
+      <c r="E60" s="3">
         <v>10068000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9585000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10810000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9916000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9735000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9553000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9399000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9241000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8366300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8254500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8454200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8540000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8980700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8388500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8959300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8750100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8372200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7593600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7738000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7319800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7007900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6716500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7168100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6717900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6625000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6932000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>6101500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>6103200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6500200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>6750200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>6641000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>6588700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>6046200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>5983000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>6140300</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>6095900</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>5729800</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>5052300</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>5366600</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>13683000</v>
+      </c>
+      <c r="E61" s="3">
         <v>14061000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>13676000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12546000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>13409000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>13244000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12345000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12797000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12351000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>12904200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>12765500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11399600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11004000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10891600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10349900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10263300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>10066900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>10608800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>10593400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>10645400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>10588200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>11741100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>12463300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>12422800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>12902500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>10023300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>8092900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>8637700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>8122100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>8134500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>8019800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7914300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>6956600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>8218700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>7712400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>8426400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>7660900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>8026600</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>8313700</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>7843500</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>703000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1177000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1231000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1226000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>738000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1081000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1054000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1115000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>591000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>995400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>979400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>958600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>517000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1009000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1878900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1841800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1854500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1988200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1986100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2012000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1918000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1864200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1847300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1816700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1815100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1723600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1785600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1729600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1203300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1169200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1221200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1311300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1980400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1977100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>2221800</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1533600</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1535500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>1753700</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>1709200</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>1717100</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6865,8 +7014,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6987,8 +7139,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7109,130 +7264,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25731000</v>
+      </c>
+      <c r="E66" s="3">
         <v>25686000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>24843000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>24933000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>24917000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>24402000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>23289000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>23644000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>23026000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>22578800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>22303200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>21112400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>20779000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>21093700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>20650600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>21095600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>20703400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>21002300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>20205700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>20429600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>19860600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>20647700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>21063100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>21441500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>21469700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>18403400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>16844500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>16501800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>15463900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>15838900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>16026500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>15903500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>15563400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>16277900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>15950800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>16183300</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>15375100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>15590400</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>15154000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>15004000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7275,8 +7436,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7397,8 +7559,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7519,8 +7684,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7641,8 +7809,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7763,130 +7934,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>13748000</v>
+      </c>
+      <c r="E72" s="3">
         <v>13461000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>13383000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>13262000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>13061000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>12792000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>12649000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>12498000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>12260000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>11898800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11724300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>11560900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>11311000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>10829900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>10649300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>10757100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>10539700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>10279800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>10216600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>10288300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>10151700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>10241700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>10383500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>10546600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>10563000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>11407000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>11639700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>11486800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>11229700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>10893600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>10654700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>10592500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>10348600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>9850700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>9708300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>9638400</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>9447800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>9317400</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>9256100</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>9159900</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8007,8 +8184,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8129,8 +8309,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8251,130 +8434,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2666000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2297000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2283000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2067000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1830000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1922000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2014000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2207000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1860000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2101000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2404000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2125800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2009000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1575300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1436600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1115300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1382300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1321400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1221100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1673300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1552900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1395600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1426800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1300000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1158600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2028900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2527500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2454700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2502600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2361900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2167600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2638600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2507000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>2351200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>2268600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>2235300</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>2381500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>2330500</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>2476000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>3020800</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8495,257 +8684,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E80" s="2">
         <v>46109</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46018</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45927</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45836</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45745</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45654</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45563</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45472</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45381</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45290</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45108</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45017</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44835</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44744</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44653</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44562</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44471</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44380</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44282</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44191</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44009</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43918</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43827</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43736</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43645</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43554</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43463</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43372</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43099</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42917</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42826</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>551000</v>
+      </c>
+      <c r="E81" s="3">
         <v>340000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>389000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>476000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>531000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>401000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>406000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>490000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>612000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>425000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>415000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>503000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>733600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>429600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>141200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>465600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>510000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>303300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>167400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>378000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>151100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>88900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>67300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>216900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-618400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>383400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>453800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>535800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>440100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>267400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>431000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>448900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>330100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>284100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>367600</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>305200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>238300</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>275200</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>323900</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8788,130 +8986,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>128000</v>
+      </c>
+      <c r="E83" s="3">
         <v>270000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>272000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>269000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>116000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>255000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>249000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>235000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>104100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>224100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>218400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>216500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>94000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>221400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>190000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>188900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>201300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>193800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>191300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>186500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>195400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>177100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>184800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>180500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>247200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>186200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>185000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>187400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>187300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>184200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>204800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>187600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>201800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>193400</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>190700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>179700</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>234700</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>218300</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>237300</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>211700</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9032,8 +9234,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9154,8 +9359,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9276,8 +9484,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9398,8 +9609,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9520,130 +9734,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1175000</v>
+      </c>
+      <c r="E89" s="3">
         <v>852000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>525000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>86000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1193000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>819000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>445000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>53000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1616000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>517000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>769000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>87000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1442200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>922300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>344900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>158600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1045400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>368800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>266200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>110800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>424100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>543100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>5800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>930900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>540200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>324000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>582900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>171600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1046000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>447400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>646600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>271100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1034400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>191000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>850400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>82800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1156900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>477500</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>351000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>253900</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9686,130 +9906,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-239000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-161000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-140000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-160000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-374000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-199000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-211000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-122000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-302000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-183000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-176000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-171000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-318500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-164800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-142400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-167300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-305300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-146200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-96400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-85000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-219500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-87200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-88400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-75500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-116600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-210500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-217700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-175700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-309500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-159100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-119500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-104300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-315200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-114000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-122300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-136300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-272600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-541900</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-1200</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-284500</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9930,8 +10154,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10052,130 +10279,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-207000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-189000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-193000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-107000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-325000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-188000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-158000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-46000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-261000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-196000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1125000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-380000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-303600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-161900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-144600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-174800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-294900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-642500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-152200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-788600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-182900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-82000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-80900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-82900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-96300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-132300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-281100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-246600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-163000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-362800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-117400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-99600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-354400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-157000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-267800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-134500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-279300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-120600</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-136100</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-3048500</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10218,130 +10451,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>259000</v>
+      </c>
+      <c r="E96" s="3">
         <v>260000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>259000</v>
       </c>
       <c r="F96" s="3">
         <v>259000</v>
       </c>
       <c r="G96" s="3">
+        <v>259000</v>
+      </c>
+      <c r="H96" s="3">
         <v>248000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>249000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>252000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>251000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>250000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>252000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>253000</v>
       </c>
       <c r="N96" s="3">
         <v>253000</v>
       </c>
       <c r="O96" s="3">
+        <v>253000</v>
+      </c>
+      <c r="P96" s="3">
         <v>248600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>249100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-249000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-249300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-239100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-238500</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-240800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-240600</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-228300</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-230500</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-230000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-228700</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-228300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-229000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-199100</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-200000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-200400</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-195800</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-192000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-187200</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-187400</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-187800</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-172100</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-174900</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-176800</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-178400</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-170100</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-173300</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10462,8 +10699,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10584,8 +10824,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10706,370 +10949,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-897000</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-67000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-195000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1113000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>66000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-234000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-131000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1098000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-718000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>712000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>66000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1032900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-495600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-127100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-400400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-746000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-213400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-789800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-237700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2138500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1333700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-205200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-950800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>3377100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1535800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-255800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>62700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-897500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-429100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-579100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>68400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-998500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-102100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-382800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>72900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-912700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-225200</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-92100</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-389700</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E101" s="3">
         <v>12000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-32000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>13000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-6000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>12000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-11000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>6300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>9100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-11400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-18300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>9100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-11400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-18300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-9400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>9400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>8100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>60000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>17100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-10000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-14400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>11100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-5500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-6500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-12900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>1200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>4900</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>18600</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>54700</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-66200</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-40700</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E102" s="3">
         <v>657000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>272000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-222000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-216000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>709000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>21000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-111000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>252000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-403000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>368000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-238000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>111900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>268800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>82200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-428000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-13700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-489800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-677300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-924900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1887900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-864500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-220400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-85700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3811000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1713100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>57100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-17800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-17500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-347200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-56400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>237500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-331300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-66800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>204700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>39700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>14400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>7800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>87400</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-3159400</v>
       </c>
     </row>
